--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-02-2026.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£10.48</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£12.15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£19.75</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£22.06</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£25.47</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1463,57 +1463,57 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>£36.25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>£32.13</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>£43.29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>£35.09</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/110mm_celotex_xr4000_pir_insulation.html?search=110mm%20celotex</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>£33.99</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>£36.25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>£32.13</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>£43.29</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>£35.09</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>£56.06</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>£33.38</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>£33.14</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.99</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1019.88</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£28.55</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£48.65</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£42.55</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£48.17</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.58</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£925.79</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1,016.40</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.08</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1267.2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
